--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0003T0006Z000C1N23_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0003T0006Z000C1N23_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>40.9258485778388</v>
+        <v>6.650450393898805</v>
       </c>
       <c r="D2" t="n">
-        <v>41.0335186572506</v>
+        <v>6.667946781803224</v>
       </c>
       <c r="E2" t="n">
-        <v>9.837661182460794</v>
+        <v>1.598619942149879</v>
       </c>
       <c r="F2" t="n">
-        <v>9.792785251664988</v>
+        <v>1.591327603395561</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>42.22624326234241</v>
+        <v>6.861764530130642</v>
       </c>
       <c r="D3" t="n">
-        <v>42.3538534018401</v>
+        <v>6.882501177799016</v>
       </c>
       <c r="E3" t="n">
-        <v>9.837661182460794</v>
+        <v>1.598619942149879</v>
       </c>
       <c r="F3" t="n">
-        <v>9.792785251664988</v>
+        <v>1.591327603395561</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>54.70488169021372</v>
+        <v>8.889543274659729</v>
       </c>
       <c r="D4" t="n">
-        <v>54.84717798125944</v>
+        <v>8.912666421954659</v>
       </c>
       <c r="E4" t="n">
-        <v>9.837661182460794</v>
+        <v>1.598619942149879</v>
       </c>
       <c r="F4" t="n">
-        <v>9.792785251664988</v>
+        <v>1.591327603395561</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>36.17109963856038</v>
+        <v>5.877803691266063</v>
       </c>
       <c r="D5" t="n">
-        <v>36.14584331623953</v>
+        <v>5.873699538888924</v>
       </c>
       <c r="E5" t="n">
-        <v>9.837661182460794</v>
+        <v>1.598619942149879</v>
       </c>
       <c r="F5" t="n">
-        <v>9.792785251664988</v>
+        <v>1.591327603395561</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>28.06364504802724</v>
+        <v>4.560342320304426</v>
       </c>
       <c r="D6" t="n">
-        <v>28.20587775409964</v>
+        <v>4.583455135041191</v>
       </c>
       <c r="E6" t="n">
-        <v>9.837661182460794</v>
+        <v>1.598619942149879</v>
       </c>
       <c r="F6" t="n">
-        <v>9.792785251664988</v>
+        <v>1.591327603395561</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>53.40234978239715</v>
+        <v>8.677881839639538</v>
       </c>
       <c r="D7" t="n">
-        <v>53.3282222908611</v>
+        <v>8.665836122264929</v>
       </c>
       <c r="E7" t="n">
-        <v>9.837661182460794</v>
+        <v>1.598619942149879</v>
       </c>
       <c r="F7" t="n">
-        <v>9.792785251664988</v>
+        <v>1.591327603395561</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>25.45687474620345</v>
+        <v>4.13674214625806</v>
       </c>
       <c r="D8" t="n">
-        <v>25.57877629639177</v>
+        <v>4.156551148163662</v>
       </c>
       <c r="E8" t="n">
-        <v>9.837661182460794</v>
+        <v>1.598619942149879</v>
       </c>
       <c r="F8" t="n">
-        <v>9.792785251664988</v>
+        <v>1.591327603395561</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>43.99818825739738</v>
+        <v>7.149705591827074</v>
       </c>
       <c r="D9" t="n">
-        <v>43.90102268573275</v>
+        <v>7.133916186431572</v>
       </c>
       <c r="E9" t="n">
-        <v>9.837661182460794</v>
+        <v>1.598619942149879</v>
       </c>
       <c r="F9" t="n">
-        <v>9.792785251664988</v>
+        <v>1.591327603395561</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>38.75314466898442</v>
+        <v>6.297386008709968</v>
       </c>
       <c r="D10" t="n">
-        <v>38.78127057651147</v>
+        <v>6.301956468683113</v>
       </c>
       <c r="E10" t="n">
-        <v>9.837661182460794</v>
+        <v>1.598619942149879</v>
       </c>
       <c r="F10" t="n">
-        <v>9.792785251664988</v>
+        <v>1.591327603395561</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>31.64948982182866</v>
+        <v>5.143042096047158</v>
       </c>
       <c r="D11" t="n">
-        <v>31.63704872423138</v>
+        <v>5.141020417687599</v>
       </c>
       <c r="E11" t="n">
-        <v>9.837661182460794</v>
+        <v>1.598619942149879</v>
       </c>
       <c r="F11" t="n">
-        <v>9.792785251664988</v>
+        <v>1.591327603395561</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>42.66856559293305</v>
+        <v>6.93364190885162</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52844651801529</v>
+        <v>6.910872559177484</v>
       </c>
       <c r="E12" t="n">
-        <v>9.837661182460794</v>
+        <v>1.598619942149879</v>
       </c>
       <c r="F12" t="n">
-        <v>9.792785251664988</v>
+        <v>1.591327603395561</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>57.82031408630599</v>
+        <v>9.395801039024724</v>
       </c>
       <c r="D13" t="n">
-        <v>57.67813508914563</v>
+        <v>9.372696951986164</v>
       </c>
       <c r="E13" t="n">
-        <v>9.837661182460794</v>
+        <v>1.598619942149879</v>
       </c>
       <c r="F13" t="n">
-        <v>9.792785251664988</v>
+        <v>1.591327603395561</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
